--- a/data/trans_orig/P21D4_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D4_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psicólogo) en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psicólogo) en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>208856</t>
+          <t>209048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>223170</t>
+          <t>222769</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>295081</t>
+          <t>294762</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>311478</t>
+          <t>311335</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>509557</t>
+          <t>510007</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>530888</t>
+          <t>531118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>20692</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>31368</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26541</t>
+          <t>26549</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46952</t>
+          <t>45928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>439514</t>
+          <t>438267</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1067403</t>
+          <t>1067840</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>846695</t>
+          <t>848593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>881868</t>
+          <t>883982</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1164264</t>
+          <t>1110392</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1930172</t>
+          <t>1931084</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40478</t>
+          <t>40031</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>672122</t>
+          <t>675670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43233</t>
+          <t>43139</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74316</t>
+          <t>73359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100161</t>
+          <t>99002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>877853</t>
+          <t>931840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16632</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>18293</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>262261</t>
+          <t>264112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>288631</t>
+          <t>289014</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>274093</t>
+          <t>275289</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>294248</t>
+          <t>293973</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>545195</t>
+          <t>545657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>577937</t>
+          <t>579082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>15765</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40816</t>
+          <t>39290</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>13467</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30619</t>
+          <t>29211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>34376</t>
+          <t>34196</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>63731</t>
+          <t>64701</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13016</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>789265</t>
+          <t>825859</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1559937</t>
+          <t>1562255</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1433903</t>
+          <t>1432549</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1477424</t>
+          <t>1476012</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2150638</t>
+          <t>2110100</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3013606</t>
+          <t>3013631</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81198</t>
+          <t>78293</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>865717</t>
+          <t>821942</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83990</t>
+          <t>84313</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122359</t>
+          <t>121877</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>186182</t>
+          <t>186038</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1062450</t>
+          <t>1111427</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21297</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26457</t>
+          <t>26351</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38520</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>21558</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,47 +2826,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>16447</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>10569</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>26187</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>16447</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>10315</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>25292</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D4_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D4_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>217562</t>
+          <t>239737</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>209048</t>
+          <t>231036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>222769</t>
+          <t>245725</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>303829</t>
+          <t>326490</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>294762</t>
+          <t>316452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>311335</t>
+          <t>334669</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>521390</t>
+          <t>566227</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>510007</t>
+          <t>553426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>531118</t>
+          <t>575905</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11787</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23632</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>18524</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31368</t>
+          <t>34294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>35420</t>
+          <t>38259</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26549</t>
+          <t>29443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45928</t>
+          <t>50735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>528</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9860</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>335993</t>
+          <t>361805</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335993</t>
+          <t>361805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>335993</t>
+          <t>361805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>566870</t>
+          <t>615460</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>566870</t>
+          <t>615460</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>566870</t>
+          <t>615460</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>828874</t>
+          <t>911528</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>438267</t>
+          <t>894066</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1067840</t>
+          <t>925061</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>863988</t>
+          <t>902458</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>848593</t>
+          <t>885848</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>883982</t>
+          <t>916058</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1692863</t>
+          <t>1813986</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1110392</t>
+          <t>1788356</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1931084</t>
+          <t>1835294</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>280890</t>
+          <t>40494</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40031</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>675670</t>
+          <t>57327</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>58681</t>
+          <t>65815</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43139</t>
+          <t>53129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73359</t>
+          <t>81330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>339571</t>
+          <t>106308</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99002</t>
+          <t>86590</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>931840</t>
+          <t>130809</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>12443</t>
+          <t>14530</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>23354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18293</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>277461</t>
+          <t>312709</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>264112</t>
+          <t>294099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>289014</t>
+          <t>324446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>286679</t>
+          <t>315487</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>275289</t>
+          <t>303644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>293973</t>
+          <t>323433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>564141</t>
+          <t>628195</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>545657</t>
+          <t>607329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>579082</t>
+          <t>642822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26413</t>
+          <t>27853</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39290</t>
+          <t>44571</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20859</t>
+          <t>22279</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13467</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29211</t>
+          <t>32746</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>47272</t>
+          <t>50132</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>34196</t>
+          <t>37014</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64701</t>
+          <t>66749</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15977</t>
+          <t>12549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>692</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,22 +2272,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1323897</t>
+          <t>1463974</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>825859</t>
+          <t>1437711</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1562255</t>
+          <t>1482653</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1454497</t>
+          <t>1544434</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1432549</t>
+          <t>1521654</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1476012</t>
+          <t>1562526</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2778394</t>
+          <t>3008408</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2110100</t>
+          <t>2974519</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3013631</t>
+          <t>3037551</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>319090</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78293</t>
+          <t>61450</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>821942</t>
+          <t>106465</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>103172</t>
+          <t>113957</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84313</t>
+          <t>97534</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121877</t>
+          <t>134191</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>422262</t>
+          <t>194698</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>186038</t>
+          <t>167802</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1111427</t>
+          <t>224892</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11825</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21194</t>
+          <t>21291</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26351</t>
+          <t>27190</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16991</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>41170</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2771,22 +2771,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7837</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>22911</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>17667</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>11914</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>26560</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>16447</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>10569</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>26187</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1585593</t>
+          <t>1689563</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1585593</t>
+          <t>1689563</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1585593</t>
+          <t>1689563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3243787</t>
+          <t>3249937</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3243787</t>
+          <t>3249937</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3243787</t>
+          <t>3249937</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
